--- a/연구코드/results/feature_selection/gangnam/step3_univariate.xlsx
+++ b/연구코드/results/feature_selection/gangnam/step3_univariate.xlsx
@@ -145,22 +145,22 @@
     <t>wavelet_cD3_energy</t>
   </si>
   <si>
+    <t>spectral_spread</t>
+  </si>
+  <si>
+    <t>spectral_centroid</t>
+  </si>
+  <si>
     <t>range</t>
   </si>
   <si>
+    <t>fft_mag_mean</t>
+  </si>
+  <si>
+    <t>peak_count</t>
+  </si>
+  <si>
     <t>peak_mean_width</t>
-  </si>
-  <si>
-    <t>peak_count</t>
-  </si>
-  <si>
-    <t>spectral_centroid</t>
-  </si>
-  <si>
-    <t>fft_mag_mean</t>
-  </si>
-  <si>
-    <t>spectral_spread</t>
   </si>
 </sst>
 </file>
@@ -854,7 +854,7 @@
         <v>-0.1082585364950464</v>
       </c>
       <c r="D24">
-        <v>9.033919250475505E-06</v>
+        <v>9.033919250475503E-06</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1008,7 +1008,7 @@
         <v>0.135979414860015</v>
       </c>
       <c r="D35">
-        <v>2.332423270366468E-08</v>
+        <v>2.332423270366469E-08</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1089,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="C41">
-        <v>-0.009061067721921497</v>
+        <v>0.07275059108621751</v>
       </c>
       <c r="D41">
-        <v>0.7110396676887148</v>
+        <v>0.00289870113315105</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1103,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <v>0.2482953503862996</v>
+        <v>0.1911693714837015</v>
       </c>
       <c r="D42">
-        <v>6.140762423516477E-25</v>
+        <v>3.055303258732452E-15</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="C43">
-        <v>0.06034229731844862</v>
+        <v>-0.009061067721921497</v>
       </c>
       <c r="D43">
-        <v>0.01353838177728521</v>
+        <v>0.7110396676887148</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1131,10 +1131,10 @@
         <v>0</v>
       </c>
       <c r="C44">
-        <v>0.1911693714837015</v>
+        <v>-0.03818823497274026</v>
       </c>
       <c r="D44">
-        <v>3.055303258732452E-15</v>
+        <v>0.1183217145704403</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="C45">
-        <v>-0.03818823497274026</v>
+        <v>0.06034229731844862</v>
       </c>
       <c r="D45">
-        <v>0.1183217145704403</v>
+        <v>0.01353838177728521</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="C46">
-        <v>0.07275059108621751</v>
+        <v>0.2482953503862996</v>
       </c>
       <c r="D46">
-        <v>0.00289870113315105</v>
+        <v>6.140762423516477E-25</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/feature_selection/gangnam/step3_univariate.xlsx
+++ b/연구코드/results/feature_selection/gangnam/step3_univariate.xlsx
@@ -145,22 +145,22 @@
     <t>wavelet_cD3_energy</t>
   </si>
   <si>
+    <t>range</t>
+  </si>
+  <si>
+    <t>peak_mean_width</t>
+  </si>
+  <si>
+    <t>peak_count</t>
+  </si>
+  <si>
+    <t>spectral_centroid</t>
+  </si>
+  <si>
+    <t>fft_mag_mean</t>
+  </si>
+  <si>
     <t>spectral_spread</t>
-  </si>
-  <si>
-    <t>spectral_centroid</t>
-  </si>
-  <si>
-    <t>range</t>
-  </si>
-  <si>
-    <t>fft_mag_mean</t>
-  </si>
-  <si>
-    <t>peak_count</t>
-  </si>
-  <si>
-    <t>peak_mean_width</t>
   </si>
 </sst>
 </file>
@@ -854,7 +854,7 @@
         <v>-0.1082585364950464</v>
       </c>
       <c r="D24">
-        <v>9.033919250475503E-06</v>
+        <v>9.033919250475505E-06</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1008,7 +1008,7 @@
         <v>0.135979414860015</v>
       </c>
       <c r="D35">
-        <v>2.332423270366469E-08</v>
+        <v>2.332423270366468E-08</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1089,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0.07275059108621751</v>
+        <v>-0.009061067721921497</v>
       </c>
       <c r="D41">
-        <v>0.00289870113315105</v>
+        <v>0.7110396676887148</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1103,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <v>0.1911693714837015</v>
+        <v>0.2482953503862996</v>
       </c>
       <c r="D42">
-        <v>3.055303258732452E-15</v>
+        <v>6.140762423516477E-25</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="C43">
-        <v>-0.009061067721921497</v>
+        <v>0.06034229731844862</v>
       </c>
       <c r="D43">
-        <v>0.7110396676887148</v>
+        <v>0.01353838177728521</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1131,10 +1131,10 @@
         <v>0</v>
       </c>
       <c r="C44">
-        <v>-0.03818823497274026</v>
+        <v>0.1911693714837015</v>
       </c>
       <c r="D44">
-        <v>0.1183217145704403</v>
+        <v>3.055303258732452E-15</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="C45">
-        <v>0.06034229731844862</v>
+        <v>-0.03818823497274026</v>
       </c>
       <c r="D45">
-        <v>0.01353838177728521</v>
+        <v>0.1183217145704403</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="C46">
-        <v>0.2482953503862996</v>
+        <v>0.07275059108621751</v>
       </c>
       <c r="D46">
-        <v>6.140762423516477E-25</v>
+        <v>0.00289870113315105</v>
       </c>
     </row>
   </sheetData>
